--- a/tame_output/ON/bt/strategyON_20240107.xlsx
+++ b/tame_output/ON/bt/strategyON_20240107.xlsx
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
     </row>
@@ -921,21 +921,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.3%</t>
+          <t>102.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.1%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.9%</t>
+          <t>131.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.6%</t>
+          <t>125.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1834"/>
+  <dimension ref="A1:G1835"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.318677134145077</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43743,6 +43743,29 @@
       </c>
       <c r="G1834" t="n">
         <v>4.48240263842715</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" s="2" t="n">
+        <v>45297</v>
+      </c>
+      <c r="B1835" t="n">
+        <v>3.320540153593092</v>
+      </c>
+      <c r="C1835" t="n">
+        <v>3.138175778137954</v>
+      </c>
+      <c r="D1835" t="n">
+        <v>1.613362209504898</v>
+      </c>
+      <c r="E1835" t="n">
+        <v>3.783164237626166</v>
+      </c>
+      <c r="F1835" t="n">
+        <v>2.238316257071205</v>
+      </c>
+      <c r="G1835" t="n">
+        <v>4.481165532380678</v>
       </c>
     </row>
   </sheetData>
